--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N137_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N137_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.23484789791949</v>
+        <v>2.475662783411917</v>
       </c>
       <c r="D2" t="n">
-        <v>15.3699220279636</v>
+        <v>2.497612329544086</v>
       </c>
       <c r="E2" t="n">
-        <v>23.9426636131139</v>
+        <v>3.89068283713101</v>
       </c>
       <c r="F2" t="n">
-        <v>23.86995031008612</v>
+        <v>3.878866925388995</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00845175934782</v>
+        <v>4.226373410894021</v>
       </c>
       <c r="D3" t="n">
-        <v>26.16916488088947</v>
+        <v>4.252489293144539</v>
       </c>
       <c r="E3" t="n">
-        <v>23.9426636131139</v>
+        <v>3.89068283713101</v>
       </c>
       <c r="F3" t="n">
-        <v>23.86995031008612</v>
+        <v>3.878866925388995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.22798540018997</v>
+        <v>12.71204762753087</v>
       </c>
       <c r="D4" t="n">
-        <v>78.18634089700602</v>
+        <v>12.70528039576348</v>
       </c>
       <c r="E4" t="n">
-        <v>23.9426636131139</v>
+        <v>3.89068283713101</v>
       </c>
       <c r="F4" t="n">
-        <v>23.86995031008612</v>
+        <v>3.878866925388995</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.32919529998501</v>
+        <v>5.578494236247565</v>
       </c>
       <c r="D5" t="n">
-        <v>34.37146481805965</v>
+        <v>5.585363032934693</v>
       </c>
       <c r="E5" t="n">
-        <v>23.9426636131139</v>
+        <v>3.89068283713101</v>
       </c>
       <c r="F5" t="n">
-        <v>23.86995031008612</v>
+        <v>3.878866925388995</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
